--- a/Lupus In Fabula — Modello Finanziario.xlsx
+++ b/Lupus In Fabula — Modello Finanziario.xlsx
@@ -8,10 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="📋 Assunzioni" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="💶 Revenue" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="🎙️ ElevenLabs" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="📈 Scenari" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="💳 Pagamenti" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="📋 Assunzioni" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="💶 Revenue" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="🎙️ ElevenLabs" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="📈 Scenari" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="170">
+  <si>
+    <t xml:space="preserve">🐺  LUPUS IN FABULA — Registro Pagamenti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tutti i costi reali sostenuti — aggiornato ad ogni pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descrizione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importo (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Developer Program (abbonamento annuale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastruttura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ In elaborazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€99/anno · rinnovo apr 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTALE SPESE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggiornato automaticamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legenda stato:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ In elaborazione  |  ✅ Confermato  |  ❌ Rimborsato / Annullato</t>
+  </si>
   <si>
     <t xml:space="preserve">🐺  LUPUS IN FABULA — Modello Finanziario</t>
   </si>
@@ -43,7 +95,7 @@
     <t xml:space="preserve">Pass Narratore (una tantum)</t>
   </si>
   <si>
-    <t xml:space="preserve">Voce ElevenLabs premium, Daniel/Adam/Arnold/custom</t>
+    <t xml:space="preserve">Pack voci pre-registrate — acquisto unico, nessun costo API</t>
   </si>
   <si>
     <t xml:space="preserve">Bundle Completo</t>
@@ -115,63 +167,39 @@
     <t xml:space="preserve">Non tutti comprano tutti i pack</t>
   </si>
   <si>
-    <t xml:space="preserve">  🎙️ ELEVENLABS — Costi API</t>
+    <t xml:space="preserve">  🎙️ ELEVENLABS — Non applicabile (voci pre-registrate)</t>
   </si>
   <si>
     <t xml:space="preserve">Caratteri per narrazione (media)</t>
   </si>
   <si>
-    <t xml:space="preserve">Una fase notturna tipica = ~180 char</t>
+    <t xml:space="preserve">N/A — voci pre-registrate</t>
   </si>
   <si>
     <t xml:space="preserve">Narrazioni per partita</t>
   </si>
   <si>
-    <t xml:space="preserve">Apertura, lupi, veggente, guardia, alba, giorno, voto, chiusura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Partite al mese per utente Pass attivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Media: 2-3 serate/mese con EL attivo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — soglia Creator (char/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">$22/mese — sufficiente per ~55 utenti Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — costo Creator (€/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">~$22 → ~€20 al cambio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — soglia Pro (char/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">$99/mese — sufficiente per ~278 utenti Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — costo Pro (€/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">~$99 → ~€91 al cambio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — soglia Scale (char/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">$330/mese — ~1.111 utenti Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piano EL — costo Scale (€/mese)</t>
   </si>
   <si>
-    <t xml:space="preserve">~$330 → ~€303 al cambio</t>
-  </si>
-  <si>
     <t xml:space="preserve">  🔧 ALTRI COSTI FISSI (€/mese)</t>
   </si>
   <si>
@@ -187,10 +215,10 @@
     <t xml:space="preserve">€23 ÷ 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlify Pro (se supera free tier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$19/mese — free fino a 100GB bandwidth</t>
+    <t xml:space="preserve">Vercel Pro (se supera free tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$20/mese — free tier generoso</t>
   </si>
   <si>
     <t xml:space="preserve">RevenueCat (gratis fino a $2.5k MRR)</t>
@@ -232,9 +260,6 @@
     <t xml:space="preserve">Anno 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
     <t xml:space="preserve">  👥 BASE UTENTI</t>
   </si>
   <si>
@@ -259,7 +284,7 @@
     <t xml:space="preserve">MAU × conv. pack × pack medi × prezzo unitario</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pass Narratore — ricavi lordi</t>
+    <t xml:space="preserve">  Pack Narratore — ricavi lordi</t>
   </si>
   <si>
     <t xml:space="preserve">MAU × conv. pass × prezzo</t>
@@ -292,10 +317,10 @@
     <t xml:space="preserve">  📉 COSTI OPERATIVI (annui)</t>
   </si>
   <si>
-    <t xml:space="preserve">  ElevenLabs API (piano auto da utilizzo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto: Creator/Pro/Scale in base agli utenti Pass</t>
+    <t xml:space="preserve">  ElevenLabs API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€0 — voci pre-registrate, nessun costo API</t>
   </si>
   <si>
     <t xml:space="preserve">  Apple Developer (€99/anno)</t>
@@ -313,7 +338,7 @@
     <t xml:space="preserve">Solo primo anno</t>
   </si>
   <si>
-    <t xml:space="preserve">  Netlify Pro</t>
+    <t xml:space="preserve">  Vercel Pro</t>
   </si>
   <si>
     <t xml:space="preserve">Se supera free tier (100GB bandwidth)</t>
@@ -358,36 +383,27 @@
     <t xml:space="preserve">Revenue netti ÷ MAU (annuo)</t>
   </si>
   <si>
-    <t xml:space="preserve">🎙️  CALCOLATORE COSTI ELEVENLABS — Lupus in Fabula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  📐 CONSUMI STIMATI</t>
+    <t xml:space="preserve">🎙️  NARRATORE AUDIO — Costi API azzerati (voci pre-registrate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ✅ COSTO API: €0/mese — Voci Pre-Registrate</t>
   </si>
   <si>
     <t xml:space="preserve">Utenti con Pass Narratore attivo (mensili)</t>
   </si>
   <si>
-    <t xml:space="preserve">Modifica per simulare crescita</t>
+    <t xml:space="preserve">€0 — tutte le frasi del narratore sono .mp3 pre-registrati</t>
   </si>
   <si>
     <t xml:space="preserve">Partite al mese per utente Pass</t>
   </si>
   <si>
-    <t xml:space="preserve">Media serate con EL attivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fasi notturne tipiche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~180 char per frase del narratore</t>
+    <t xml:space="preserve">N/A — costo zero</t>
   </si>
   <si>
     <t xml:space="preserve">▶  TOTALE CARATTERI / MESE</t>
   </si>
   <si>
-    <t xml:space="preserve">0 char / nessun overage — Gratis fino a 10.000 char/mese</t>
-  </si>
-  <si>
     <t xml:space="preserve">  💳 PIANI ELEVENLABS (prezzi 2025)</t>
   </si>
   <si>
@@ -436,25 +452,28 @@
     <t xml:space="preserve">Piano consigliato per il tuo utilizzo</t>
   </si>
   <si>
+    <t xml:space="preserve">Free ✅ — €0/mese</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calcolato automaticamente dai tuoi input</t>
   </si>
   <si>
     <t xml:space="preserve">Costo mensile stimato (€)</t>
   </si>
   <si>
-    <t xml:space="preserve">💡 NOTA SUL MODELLO DI COSTO:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Con il modello attuale (Netlify proxy), la chiave EL è SERVER-SIDE: TU paghi per tutti gli utenti Pass.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Alternativa A: Pass Narratore = utenti portano la propria chiave EL (costo zero per te, ma più friction per l'utente).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Alternativa B: Pass Narratore = abbonamento mensile che copre i costi EL (€2,99/mese invece di €4,99 una tantum).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Raccomandazione: mantieni chiave server-side e monitora il costo EL mensile. Se supera 30% del revenue Pass → rivedi pricing.</t>
+    <t xml:space="preserve">💡 MODELLO ATTUALE: Voci Pre-Registrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Tutte le frasi del narratore sono file .mp3 inclusi nel bundle dell'app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Costo ElevenLabs API = €0. Il Pack Narratore è margine puro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Nessun abbonamento, nessun costo variabile al crescere degli utenti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Se in futuro si aggiungono voci, si può creare un nuovo IAP 'Pack Voci'.</t>
   </si>
   <si>
     <t xml:space="preserve">📈  LUPUS IN FABULA — Confronto Scenari  (Conservative / Realistic / Optimistic)</t>
@@ -496,7 +515,7 @@
     <t xml:space="preserve">Revenue Netti (€/anno)</t>
   </si>
   <si>
-    <t xml:space="preserve">Costi EL + Infra (€/anno)</t>
+    <t xml:space="preserve">Costi Infra (€/anno)</t>
   </si>
   <si>
     <t xml:space="preserve">UTILE NETTO (€/anno)</t>
@@ -521,19 +540,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;;\(#,##0.00&quot; €)&quot;;\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="171" formatCode="#,##0&quot; €&quot;;\(#,##0&quot; €)&quot;;\-"/>
-    <numFmt numFmtId="172" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="173" formatCode="\€#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="\€#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot; €&quot;;\(#,##0.00&quot; €)&quot;;\-"/>
+    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
+    <numFmt numFmtId="172" formatCode="#,##0&quot; €&quot;;\(#,##0&quot; €)&quot;;\-"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,7 +577,46 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <color rgb="FFC9A84C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFE67E22"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -573,6 +630,53 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF777777"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFE8E8E8"/>
@@ -597,7 +701,16 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="9"/>
+      <strike val="true"/>
+      <sz val="10"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -693,22 +806,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
@@ -781,7 +878,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -790,8 +887,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0B0A14"/>
+        <bgColor rgb="FF0D1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A2E"/>
+        <bgColor rgb="FF0D1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F5EE"/>
+        <bgColor rgb="FFFFF0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF0FFF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E6B8"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF0D1117"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor rgb="FF0B0A14"/>
       </patternFill>
     </fill>
     <fill>
@@ -832,12 +959,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5E6B8"/>
-        <bgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7B241C"/>
         <bgColor rgb="FF800000"/>
       </patternFill>
@@ -852,12 +973,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF0FFF0"/>
         <bgColor rgb="FFE8FFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF0FFF0"/>
       </patternFill>
     </fill>
     <fill>
@@ -949,6 +1064,21 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
         <color rgb="FFEEEEEE"/>
       </left>
       <right style="thin">
@@ -992,21 +1122,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1033,7 +1148,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="143">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1043,474 +1158,566 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="13" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="17" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="40" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="18" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1532,11 +1739,11 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FFF0FFF0"/>
       <rgbColor rgb="FF8B0000"/>
       <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF1A1A2E"/>
+      <rgbColor rgb="FF777777"/>
       <rgbColor rgb="FF6A0DAD"/>
       <rgbColor rgb="FF1E5C1E"/>
       <rgbColor rgb="FFCCCCCC"/>
@@ -1549,15 +1756,15 @@
       <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFC0D8FF"/>
-      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF0B0A14"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFB8FFB8"/>
-      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FFF8F5EE"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFFFF0F0"/>
       <rgbColor rgb="FFE8F5E9"/>
       <rgbColor rgb="FFD0FFD0"/>
       <rgbColor rgb="FFF5E6B8"/>
@@ -1566,11 +1773,11 @@
       <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FFFFD8D8"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FFF0FFF0"/>
       <rgbColor rgb="FFE8F0FF"/>
+      <rgbColor rgb="FFC9A84C"/>
       <rgbColor rgb="FFFDEDEC"/>
       <rgbColor rgb="FFC4931A"/>
-      <rgbColor rgb="FFFFF0F0"/>
+      <rgbColor rgb="FFE67E22"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF1E3A5F"/>
@@ -1764,6 +1971,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <f aca="false">SUM(C5:C6)</f>
+        <v>99</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFC4931A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1776,362 +2110,362 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="27" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="27" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="C22" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="23" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="23" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>91</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>303</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>55</v>
+      <c r="C35" s="24" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="13" t="n">
+      <c r="A36" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>57</v>
+      <c r="C36" s="24" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="6" t="n">
+      <c r="A37" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>59</v>
+      <c r="C37" s="24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>60</v>
+      <c r="A39" s="36" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>61</v>
+      <c r="A40" s="37" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="s">
-        <v>62</v>
+      <c r="A41" s="38" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
-        <v>63</v>
+      <c r="A42" s="39" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2153,7 +2487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1E8449"/>
@@ -2167,471 +2501,468 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="A2" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="A3" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="23" t="n">
+      <c r="A4" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="45" t="n">
         <f aca="false">'📋 Assunzioni'!B12</f>
         <v>15000</v>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="45" t="n">
         <f aca="false">'📋 Assunzioni'!B12+'📋 Assunzioni'!B13</f>
         <v>75000</v>
       </c>
-      <c r="D4" s="23" t="n">
+      <c r="D4" s="45" t="n">
         <f aca="false">'📋 Assunzioni'!B12+'📋 Assunzioni'!B13+'📋 Assunzioni'!B14</f>
         <v>225000</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="E4" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="25" t="n">
+      <c r="A5" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="47" t="n">
         <f aca="false">ROUND('📋 Assunzioni'!B12*'📋 Assunzioni'!B15,0)</f>
         <v>6000</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="47" t="n">
         <f aca="false">ROUND(('📋 Assunzioni'!B12+'📋 Assunzioni'!B13)*'📋 Assunzioni'!B15,0)</f>
         <v>30000</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="47" t="n">
         <f aca="false">ROUND(('📋 Assunzioni'!B12+'📋 Assunzioni'!B13+'📋 Assunzioni'!B14)*'📋 Assunzioni'!B15,0)</f>
         <v>90000</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
+      <c r="E5" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="A6" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="26" t="n">
+      <c r="A7" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="48" t="n">
         <f aca="false">ROUND(B5*'📋 Assunzioni'!B16*'📋 Assunzioni'!B19*'📋 Assunzioni'!B5,2)</f>
         <v>1170.12</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="48" t="n">
         <f aca="false">ROUND(C5*'📋 Assunzioni'!B16*'📋 Assunzioni'!B19*'📋 Assunzioni'!B5,2)</f>
         <v>5850.6</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="48" t="n">
         <f aca="false">ROUND(D5*'📋 Assunzioni'!B16*'📋 Assunzioni'!B19*'📋 Assunzioni'!B5,2)</f>
         <v>17551.8</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="E7" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="26" t="n">
+      <c r="A8" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="48" t="n">
         <f aca="false">ROUND(B5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B6,2)</f>
         <v>1197.6</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="48" t="n">
         <f aca="false">ROUND(C5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B6,2)</f>
         <v>5988</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="48" t="n">
         <f aca="false">ROUND(D5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B6,2)</f>
         <v>17964</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
+      <c r="E8" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="26" t="n">
+      <c r="A9" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="48" t="n">
         <f aca="false">ROUND(B5*'📋 Assunzioni'!B18*'📋 Assunzioni'!B7,2)</f>
         <v>958.8</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="48" t="n">
         <f aca="false">ROUND(C5*'📋 Assunzioni'!B18*'📋 Assunzioni'!B7,2)</f>
         <v>4794</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="48" t="n">
         <f aca="false">ROUND(D5*'📋 Assunzioni'!B18*'📋 Assunzioni'!B7,2)</f>
         <v>14382</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+      <c r="E9" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="28" t="n">
+      <c r="A10" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="50" t="n">
         <f aca="false">SUM(B7:B9)</f>
         <v>3326.52</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="50" t="n">
         <f aca="false">SUM(C7:C9)</f>
         <v>16632.6</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="50" t="n">
         <f aca="false">SUM(D7:D9)</f>
         <v>49897.8</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
+      <c r="E10" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="29" t="n">
+      <c r="A11" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="51" t="n">
         <f aca="false">-ROUND(B10*'📋 Assunzioni'!B9,2)</f>
         <v>-498.98</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="51" t="n">
         <f aca="false">-ROUND(C10*'📋 Assunzioni'!B9,2)</f>
         <v>-2494.89</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="51" t="n">
         <f aca="false">-ROUND(D10*'📋 Assunzioni'!B8,2)</f>
         <v>-14969.34</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
+      <c r="E11" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="31" t="n">
+      <c r="A12" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <f aca="false">B10+B11</f>
         <v>2827.54</v>
       </c>
-      <c r="C12" s="31" t="n">
+      <c r="C12" s="53" t="n">
         <f aca="false">C10+C11</f>
         <v>14137.71</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="53" t="n">
         <f aca="false">D10+D11</f>
         <v>34928.46</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
+      <c r="E12" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
+      <c r="A13" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="26" t="n">
-        <f aca="false">ROUND(IF(B5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B27,'📋 Assunzioni'!B28*12,IF(B5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B29,'📋 Assunzioni'!B30*12,'📋 Assunzioni'!B32*12)),2)</f>
-        <v>3636</v>
-      </c>
-      <c r="C14" s="26" t="n">
-        <f aca="false">ROUND(IF(C5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B27,'📋 Assunzioni'!B28*12,IF(C5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B29,'📋 Assunzioni'!B30*12,'📋 Assunzioni'!B32*12)),2)</f>
+      <c r="A14" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="26" t="n">
-        <f aca="false">ROUND(IF(D5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B27,'📋 Assunzioni'!B28*12,IF(D5*'📋 Assunzioni'!B17*'📋 Assunzioni'!B24*'📋 Assunzioni'!B23*'📋 Assunzioni'!B22&lt;='📋 Assunzioni'!B29,'📋 Assunzioni'!B30*12,'📋 Assunzioni'!B32*12)),2)</f>
+      <c r="C14" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
+      <c r="D14" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="26" t="n">
+      <c r="A15" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B35*12</f>
         <v>204</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B35*12</f>
         <v>204</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B35*12</f>
         <v>204</v>
       </c>
-      <c r="E15" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
+      <c r="E15" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="26" t="n">
+      <c r="A16" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B36*12</f>
         <v>0</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
+      <c r="C16" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="26" t="n">
+      <c r="A17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B37*12</f>
         <v>0</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B37*12</f>
         <v>0</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B37*12</f>
         <v>0</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="E17" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" s="26" t="n">
+      <c r="A18" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B38*12</f>
         <v>0</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="48" t="n">
         <f aca="false">IF(B12/12&gt;2300,ROUND(B12*0.01,2),0)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="48" t="n">
         <f aca="false">IF(C12/12&gt;2300,ROUND(C12*0.01,2),0)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
+      <c r="E18" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="26" t="n">
+      <c r="A19" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="48" t="n">
         <f aca="false">'📋 Assunzioni'!B39*12</f>
         <v>0</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="26" t="n">
+      <c r="C19" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="48" t="n">
         <f aca="false">ROUND(D5*0.0012*12,2)</f>
         <v>1296</v>
       </c>
-      <c r="E19" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="E19" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="34" t="n">
+      <c r="A20" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="56" t="n">
         <f aca="false">SUM(B14:B19)</f>
-        <v>3840</v>
-      </c>
-      <c r="C20" s="34" t="n">
+        <v>204</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">SUM(C14:C19)</f>
         <v>204</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="56" t="n">
         <f aca="false">SUM(D14:D19)</f>
         <v>1500</v>
       </c>
-      <c r="E20" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
+      <c r="E20" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="A21" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="31" t="n">
+      <c r="A22" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="53" t="n">
         <f aca="false">B12-B20</f>
-        <v>-1012.46</v>
-      </c>
-      <c r="C22" s="31" t="n">
+        <v>2623.54</v>
+      </c>
+      <c r="C22" s="53" t="n">
         <f aca="false">C12-C20</f>
         <v>13933.71</v>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="53" t="n">
         <f aca="false">D12-D20</f>
         <v>33428.46</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="E22" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="36" t="n">
+      <c r="A23" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="58" t="n">
         <f aca="false">IF(B12&lt;&gt;0,B22/B12,0)</f>
-        <v>-0.358070973354931</v>
-      </c>
-      <c r="C23" s="36" t="n">
+        <v>0.927852479540519</v>
+      </c>
+      <c r="C23" s="58" t="n">
         <f aca="false">IF(C12&lt;&gt;0,C22/C12,0)</f>
         <v>0.985570506114498</v>
       </c>
-      <c r="D23" s="36" t="n">
+      <c r="D23" s="58" t="n">
         <f aca="false">IF(D12&lt;&gt;0,D22/D12,0)</f>
         <v>0.95705507772172</v>
       </c>
-      <c r="E23" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="E23" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="26" t="n">
+      <c r="A24" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="48" t="n">
         <f aca="false">IF(B5&gt;0,B12/B5,0)</f>
         <v>0.471256666666667</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="48" t="n">
         <f aca="false">IF(C5&gt;0,C12/C5,0)</f>
         <v>0.471257</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="48" t="n">
         <f aca="false">IF(D5&gt;0,D12/D5,0)</f>
         <v>0.388094</v>
       </c>
-      <c r="E24" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="E24" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2670,7 +3001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF6A0DAD"/>
@@ -2685,210 +3016,207 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="A1" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>117</v>
+      <c r="B6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>118</v>
+      <c r="A7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="38" t="n">
-        <f aca="false">ROUND(B4*B5*B6*B7,0)</f>
-        <v>180000</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>120</v>
+      <c r="A8" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>124</v>
+      <c r="A11" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="41" t="n">
+      <c r="A12" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>126</v>
+      <c r="C12" s="65" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="44" t="n">
+      <c r="A13" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="45" t="s">
-        <v>128</v>
+      <c r="C13" s="68" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="41" t="n">
+      <c r="A14" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="64" t="n">
         <v>91</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>130</v>
+      <c r="C14" s="65" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="44" t="n">
+      <c r="A15" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="67" t="n">
         <v>303</v>
       </c>
-      <c r="C15" s="45" t="s">
-        <v>132</v>
+      <c r="C15" s="68" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="41" t="n">
+      <c r="A16" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="64" t="n">
         <v>1210</v>
       </c>
-      <c r="C16" s="42" t="s">
-        <v>134</v>
+      <c r="C16" s="65" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="A18" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="49" t="str">
-        <f aca="false">IF(B8&lt;=10000,"Free ✅",IF(B8&lt;=100000,"Creator — €20/mese",IF(B8&lt;=500000,"Pro — €91/mese",IF(B8&lt;=2000000,"Scale — €303/mese","Business — €1.210/mese"))))</f>
-        <v>Pro — €91/mese</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>137</v>
+      <c r="A19" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="51" t="n">
-        <f aca="false">IF(B8&lt;=10000,0,IF(B8&lt;=100000,20,IF(B8&lt;=500000,91,IF(B8&lt;=2000000,303,1210))))</f>
-        <v>91</v>
+      <c r="A20" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
+      <c r="A22" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="76" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
+      <c r="A24" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
+      <c r="A25" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
+      <c r="A26" s="76" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2912,7 +3240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFC4931A"/>
@@ -2926,379 +3254,379 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="A1" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="I2" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>148</v>
+      <c r="A2" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="I2" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" s="80" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="60" t="n">
+      <c r="A4" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="83" t="n">
         <v>5000</v>
       </c>
-      <c r="C4" s="61" t="n">
+      <c r="C4" s="84" t="n">
         <v>20000</v>
       </c>
-      <c r="D4" s="62" t="n">
+      <c r="D4" s="85" t="n">
         <v>50000</v>
       </c>
-      <c r="E4" s="63" t="n">
+      <c r="E4" s="86" t="n">
         <v>15000</v>
       </c>
-      <c r="F4" s="64" t="n">
+      <c r="F4" s="87" t="n">
         <v>60000</v>
       </c>
-      <c r="G4" s="65" t="n">
+      <c r="G4" s="88" t="n">
         <v>150000</v>
       </c>
-      <c r="H4" s="66" t="n">
+      <c r="H4" s="89" t="n">
         <v>40000</v>
       </c>
-      <c r="I4" s="67" t="n">
+      <c r="I4" s="90" t="n">
         <v>150000</v>
       </c>
-      <c r="J4" s="68" t="n">
+      <c r="J4" s="91" t="n">
         <v>400000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="60" t="n">
+      <c r="A5" s="82" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="83" t="n">
         <v>1750</v>
       </c>
-      <c r="C5" s="61" t="n">
+      <c r="C5" s="84" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="62" t="n">
+      <c r="D5" s="85" t="n">
         <v>17500</v>
       </c>
-      <c r="E5" s="63" t="n">
+      <c r="E5" s="86" t="n">
         <v>6000</v>
       </c>
-      <c r="F5" s="64" t="n">
+      <c r="F5" s="87" t="n">
         <v>24000</v>
       </c>
-      <c r="G5" s="65" t="n">
+      <c r="G5" s="88" t="n">
         <v>60000</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="89" t="n">
         <v>20000</v>
       </c>
-      <c r="I5" s="67" t="n">
+      <c r="I5" s="90" t="n">
         <v>75000</v>
       </c>
-      <c r="J5" s="68" t="n">
+      <c r="J5" s="91" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="69" t="n">
+      <c r="A6" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="92" t="n">
         <v>868</v>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="93" t="n">
         <v>3472</v>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="94" t="n">
         <v>8679</v>
       </c>
-      <c r="E6" s="72" t="n">
+      <c r="E6" s="95" t="n">
         <v>3800</v>
       </c>
-      <c r="F6" s="73" t="n">
+      <c r="F6" s="96" t="n">
         <v>15222</v>
       </c>
-      <c r="G6" s="74" t="n">
+      <c r="G6" s="97" t="n">
         <v>38055</v>
       </c>
-      <c r="H6" s="75" t="n">
+      <c r="H6" s="98" t="n">
         <v>14320</v>
       </c>
-      <c r="I6" s="76" t="n">
+      <c r="I6" s="99" t="n">
         <v>53700</v>
       </c>
-      <c r="J6" s="77" t="n">
+      <c r="J6" s="100" t="n">
         <v>142900</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="78" t="n">
+      <c r="A7" s="82" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="101" t="n">
         <v>-130</v>
       </c>
-      <c r="C7" s="79" t="n">
+      <c r="C7" s="102" t="n">
         <v>-521</v>
       </c>
-      <c r="D7" s="80" t="n">
+      <c r="D7" s="103" t="n">
         <v>-1302</v>
       </c>
-      <c r="E7" s="81" t="n">
+      <c r="E7" s="104" t="n">
         <v>-570</v>
       </c>
-      <c r="F7" s="82" t="n">
+      <c r="F7" s="105" t="n">
         <v>-2283</v>
       </c>
-      <c r="G7" s="83" t="n">
+      <c r="G7" s="106" t="n">
         <v>-11417</v>
       </c>
-      <c r="H7" s="84" t="n">
+      <c r="H7" s="107" t="n">
         <v>-2148</v>
       </c>
-      <c r="I7" s="85" t="n">
+      <c r="I7" s="108" t="n">
         <v>-8055</v>
       </c>
-      <c r="J7" s="86" t="n">
+      <c r="J7" s="109" t="n">
         <v>-42870</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="87" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="88" t="n">
+      <c r="A8" s="110" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="111" t="n">
         <v>738</v>
       </c>
-      <c r="C8" s="89" t="n">
+      <c r="C8" s="112" t="n">
         <v>2951</v>
       </c>
-      <c r="D8" s="90" t="n">
+      <c r="D8" s="113" t="n">
         <v>7377</v>
       </c>
-      <c r="E8" s="91" t="n">
+      <c r="E8" s="114" t="n">
         <v>3230</v>
       </c>
-      <c r="F8" s="92" t="n">
+      <c r="F8" s="115" t="n">
         <v>12939</v>
       </c>
-      <c r="G8" s="93" t="n">
+      <c r="G8" s="116" t="n">
         <v>26638</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="H8" s="117" t="n">
         <v>12172</v>
       </c>
-      <c r="I8" s="95" t="n">
+      <c r="I8" s="118" t="n">
         <v>45645</v>
       </c>
-      <c r="J8" s="96" t="n">
+      <c r="J8" s="119" t="n">
         <v>100030</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="78" t="n">
-        <v>219</v>
-      </c>
-      <c r="C9" s="79" t="n">
-        <v>219</v>
-      </c>
-      <c r="D9" s="80" t="n">
-        <v>240</v>
-      </c>
-      <c r="E9" s="81" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F9" s="82" t="n">
-        <v>3636</v>
-      </c>
-      <c r="G9" s="83" t="n">
-        <v>5796</v>
-      </c>
-      <c r="H9" s="84" t="n">
-        <v>3636</v>
-      </c>
-      <c r="I9" s="85" t="n">
-        <v>10884</v>
-      </c>
-      <c r="J9" s="86" t="n">
-        <v>16380</v>
+      <c r="A9" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="101" t="n">
+        <v>122</v>
+      </c>
+      <c r="C9" s="102" t="n">
+        <v>99</v>
+      </c>
+      <c r="D9" s="103" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="104" t="n">
+        <v>122</v>
+      </c>
+      <c r="F9" s="105" t="n">
+        <v>99</v>
+      </c>
+      <c r="G9" s="106" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="107" t="n">
+        <v>122</v>
+      </c>
+      <c r="I9" s="108" t="n">
+        <v>99</v>
+      </c>
+      <c r="J9" s="109" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="98" t="n">
-        <v>519</v>
-      </c>
-      <c r="C10" s="98" t="n">
-        <v>2732</v>
-      </c>
-      <c r="D10" s="98" t="n">
-        <v>7137</v>
-      </c>
-      <c r="E10" s="98" t="n">
-        <v>2138</v>
-      </c>
-      <c r="F10" s="98" t="n">
-        <v>9303</v>
-      </c>
-      <c r="G10" s="98" t="n">
-        <v>20842</v>
-      </c>
-      <c r="H10" s="98" t="n">
-        <v>8536</v>
-      </c>
-      <c r="I10" s="98" t="n">
-        <v>34761</v>
-      </c>
-      <c r="J10" s="98" t="n">
-        <v>83650</v>
+      <c r="A10" s="120" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="121" t="n">
+        <v>616</v>
+      </c>
+      <c r="C10" s="121" t="n">
+        <v>2852</v>
+      </c>
+      <c r="D10" s="121" t="n">
+        <v>7257</v>
+      </c>
+      <c r="E10" s="121" t="n">
+        <v>3108</v>
+      </c>
+      <c r="F10" s="121" t="n">
+        <v>14039</v>
+      </c>
+      <c r="G10" s="121" t="n">
+        <v>34628</v>
+      </c>
+      <c r="H10" s="121" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I10" s="121" t="n">
+        <v>45546</v>
+      </c>
+      <c r="J10" s="121" t="n">
+        <v>99530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="99" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="C11" s="100" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="D11" s="101" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="E11" s="102" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="F11" s="103" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="G11" s="104" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="H11" s="105" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="I11" s="106" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="J11" s="107" t="n">
-        <v>0.836</v>
+      <c r="A11" s="82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="122" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C11" s="123" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="D11" s="124" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="E11" s="125" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="F11" s="126" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="G11" s="127" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="H11" s="128" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I11" s="129" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="J11" s="130" t="n">
+        <v>0.995</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="108" t="n">
+      <c r="A12" s="82" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="131" t="n">
         <v>0.42</v>
       </c>
-      <c r="C12" s="109" t="n">
+      <c r="C12" s="132" t="n">
         <v>0.42</v>
       </c>
-      <c r="D12" s="110" t="n">
+      <c r="D12" s="133" t="n">
         <v>0.42</v>
       </c>
-      <c r="E12" s="111" t="n">
+      <c r="E12" s="134" t="n">
         <v>0.54</v>
       </c>
-      <c r="F12" s="112" t="n">
+      <c r="F12" s="135" t="n">
         <v>0.54</v>
       </c>
-      <c r="G12" s="113" t="n">
+      <c r="G12" s="136" t="n">
         <v>0.44</v>
       </c>
-      <c r="H12" s="114" t="n">
+      <c r="H12" s="137" t="n">
         <v>0.61</v>
       </c>
-      <c r="I12" s="115" t="n">
+      <c r="I12" s="138" t="n">
         <v>0.61</v>
       </c>
-      <c r="J12" s="116" t="n">
+      <c r="J12" s="139" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="117" t="s">
-        <v>161</v>
+      <c r="A13" s="140" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="118" t="s">
-        <v>162</v>
+      <c r="A14" s="141" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="119" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
+      <c r="A15" s="142" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="142"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="5">
